--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,6 +2517,116 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127818825</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>517119</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668200</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,6 +2626,861 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127896964</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västermoren, Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>517078</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668218</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127929383</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>517062</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668237</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127929400</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>517077</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668228</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127929414</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5002</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>517124</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668189</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127929429</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>517205</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668188</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127929425</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>517205</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668188</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127929663</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>517074</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6668246</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
+          <t>Philipp Weiss, Alec Bailey, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Alec Bailey, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3482,6 +3482,794 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128371010</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90855</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>517080</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6668206</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128370967</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90855</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>517054</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6668207</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128370986</v>
+      </c>
+      <c r="B26" t="n">
+        <v>86623</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>517070</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6668207</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128370951</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>517049</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6668217</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128370970</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90892</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>517054</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6668207</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128370989</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>517070</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6668207</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4270,6 +4270,140 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128399064</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flogberget gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>517057</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6668295</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90855</v>
+        <v>90858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>90855</v>
+        <v>90858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>86623</v>
+        <v>86624</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>90892</v>
+        <v>90895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2522,7 +2522,7 @@
         <v>127818825</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
+          <t>Philipp Weiss, Alec Bailey, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey, Philipp Weiss, Patric Engfeldt</t>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3618,59 +3618,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370967</v>
+        <v>128370986</v>
       </c>
       <c r="B25" t="n">
-        <v>90950</v>
+        <v>86716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5745</v>
+        <v>3762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517054</v>
+        <v>517070</v>
       </c>
       <c r="R25" t="n">
         <v>6668207</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3752,51 +3744,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370986</v>
+        <v>128370967</v>
       </c>
       <c r="B26" t="n">
-        <v>86716</v>
+        <v>90950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517070</v>
+        <v>517054</v>
       </c>
       <c r="R26" t="n">
         <v>6668207</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4404,6 +4404,279 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128627698</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>517145</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6668191</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128627684</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>517047</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6668253</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 + 10 + 1</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Alec Bailey, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -2632,7 +2632,7 @@
         <v>127896964</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>127929663</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90950</v>
+        <v>90962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370986</v>
       </c>
       <c r="B25" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128370967</v>
       </c>
       <c r="B26" t="n">
-        <v>90950</v>
+        <v>90962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>90964</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370986</v>
       </c>
       <c r="B25" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128370967</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>90964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86954</v>
+        <v>86956</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3618,51 +3618,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370986</v>
+        <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>86729</v>
+        <v>90964</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517070</v>
+        <v>517054</v>
       </c>
       <c r="R25" t="n">
         <v>6668207</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3744,59 +3752,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370967</v>
+        <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>90964</v>
+        <v>86729</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5745</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517054</v>
+        <v>517070</v>
       </c>
       <c r="R26" t="n">
         <v>6668207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90964</v>
+        <v>90965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3618,59 +3618,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370967</v>
+        <v>128370986</v>
       </c>
       <c r="B25" t="n">
-        <v>90964</v>
+        <v>86729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5745</v>
+        <v>3762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517054</v>
+        <v>517070</v>
       </c>
       <c r="R25" t="n">
         <v>6668207</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3752,51 +3744,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370986</v>
+        <v>128370967</v>
       </c>
       <c r="B26" t="n">
-        <v>86729</v>
+        <v>90965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517070</v>
+        <v>517054</v>
       </c>
       <c r="R26" t="n">
         <v>6668207</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90965</v>
+        <v>90992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3618,51 +3618,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370986</v>
+        <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>86729</v>
+        <v>90992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517070</v>
+        <v>517054</v>
       </c>
       <c r="R25" t="n">
         <v>6668207</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3744,59 +3752,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370967</v>
+        <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>90965</v>
+        <v>86756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5745</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517054</v>
+        <v>517070</v>
       </c>
       <c r="R26" t="n">
         <v>6668207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>90992</v>
+        <v>91002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>90992</v>
+        <v>91002</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>91029</v>
+        <v>91039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>91002</v>
+        <v>91006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>128370967</v>
       </c>
       <c r="B25" t="n">
-        <v>91002</v>
+        <v>91006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>128370986</v>
       </c>
       <c r="B26" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -3487,7 +3487,7 @@
         <v>128371010</v>
       </c>
       <c r="B24" t="n">
-        <v>91006</v>
+        <v>91011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3618,59 +3618,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370967</v>
+        <v>128370986</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>86769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5745</v>
+        <v>3762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517054</v>
+        <v>517070</v>
       </c>
       <c r="R25" t="n">
         <v>6668207</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3752,51 +3744,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370986</v>
+        <v>128370967</v>
       </c>
       <c r="B26" t="n">
-        <v>86764</v>
+        <v>91011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517070</v>
+        <v>517054</v>
       </c>
       <c r="R26" t="n">
         <v>6668207</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>128370951</v>
       </c>
       <c r="B27" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>128370970</v>
       </c>
       <c r="B28" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128370989</v>
       </c>
       <c r="B29" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128399064</v>
       </c>
       <c r="B30" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -4409,7 +4409,7 @@
         <v>128627698</v>
       </c>
       <c r="B31" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>128627684</v>
       </c>
       <c r="B32" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73111023</v>
+        <v>111615018</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517078.0599662762</v>
+        <v>517051</v>
       </c>
       <c r="R2" t="n">
-        <v>6668214.202619326</v>
+        <v>6668265</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,26 +766,7 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -816,63 +775,65 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95730048</v>
+        <v>111630399</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför gruvan, Dlr</t>
+          <t>Flogbergets gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517069.0309823108</v>
+        <v>517040</v>
       </c>
       <c r="R3" t="n">
-        <v>6668225.115636764</v>
+        <v>6668260</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,100 +881,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103883115</v>
+        <v>73111050</v>
       </c>
       <c r="B4" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3739</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flogberget gruva, nedanför vägen, Dlr</t>
+          <t>Flogberget, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517042.5217899113</v>
+        <v>517141</v>
       </c>
       <c r="R4" t="n">
-        <v>6668240.926920929</v>
+        <v>6668212</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1040,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,11 +1009,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Anders Janols</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1106,61 +1017,63 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Janols</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111452144</v>
+        <v>103883115</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3739</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, Dlr</t>
+          <t>Flogberget gruva, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517083.0152773387</v>
+        <v>517043</v>
       </c>
       <c r="R5" t="n">
-        <v>6668221.19709258</v>
+        <v>6668241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1187,22 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,7 +1125,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>mossig äldre kalkmarksskog,</t>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1233,48 +1156,51 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111614979</v>
+        <v>111615967</v>
       </c>
       <c r="B6" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>3739</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1283,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517137.0018463049</v>
+        <v>517051</v>
       </c>
       <c r="R6" t="n">
-        <v>6668196.053062852</v>
+        <v>6668265</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1316,19 +1242,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1262,26 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1355,49 +1290,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111614976</v>
+        <v>111630395</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1406,20 +1336,19 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, Dlr</t>
+          <t>Flogbergets gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517137.0018463049</v>
+        <v>517040</v>
       </c>
       <c r="R7" t="n">
-        <v>6668196.053062852</v>
+        <v>6668260</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,22 +1372,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,40 +1396,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111615967</v>
+        <v>128627684</v>
       </c>
       <c r="B8" t="n">
-        <v>85313</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,26 +1444,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, Dlr</t>
+          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517051.3886122297</v>
+        <v>517047</v>
       </c>
       <c r="R8" t="n">
-        <v>6668264.869833886</v>
+        <v>6668253</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1573,22 +1490,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 + 10 + 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmark</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1641,37 +1553,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111615018</v>
+        <v>95902482</v>
       </c>
       <c r="B9" t="n">
-        <v>90651</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1968</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1680,17 +1587,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, Dlr</t>
+          <t>Flogberget gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517051.3886122297</v>
+        <v>517023</v>
       </c>
       <c r="R9" t="n">
-        <v>6668264.869833886</v>
+        <v>6668180</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1714,22 +1621,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1744,10 +1641,29 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1756,22 +1672,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111630488</v>
+        <v>128370986</v>
       </c>
       <c r="B10" t="n">
-        <v>88068</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1779,47 +1690,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6292</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flogbergets gruvområde, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517225</v>
+        <v>517070</v>
       </c>
       <c r="R10" t="n">
-        <v>6668199</v>
+        <v>6668207</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1843,22 +1747,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1867,33 +1761,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111630395</v>
+        <v>127896964</v>
       </c>
       <c r="B11" t="n">
-        <v>85313</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,47 +1816,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3739</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flogbergets gruvområde, Dlr</t>
+          <t>Västermoren, Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517040</v>
+        <v>517078</v>
       </c>
       <c r="R11" t="n">
-        <v>6668260</v>
+        <v>6668218</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1965,22 +1872,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1989,33 +1886,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111630399</v>
+        <v>96230552</v>
       </c>
       <c r="B12" t="n">
-        <v>90651</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2023,26 +1916,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2051,19 +1944,20 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flogbergets gruvområde, Dlr</t>
+          <t>Flogberget, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517040</v>
+        <v>517088</v>
       </c>
       <c r="R12" t="n">
         <v>6668260</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2087,22 +1981,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2111,67 +1995,80 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkmarksskog bondskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111776936</v>
+        <v>111614979</v>
       </c>
       <c r="B13" t="n">
-        <v>88918</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5745</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2180,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517076</v>
+        <v>517137</v>
       </c>
       <c r="R13" t="n">
-        <v>6668201</v>
+        <v>6668196</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2210,12 +2107,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,29 +2127,10 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2261,44 +2139,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Martin Gotink</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111938715</v>
+        <v>128399382</v>
       </c>
       <c r="B14" t="n">
-        <v>89104</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2315,14 +2188,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, Dlr</t>
+          <t>Flogberget gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517051</v>
+        <v>517091</v>
       </c>
       <c r="R14" t="n">
-        <v>6668198</v>
+        <v>6668255</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2349,12 +2222,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2374,7 +2247,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmark. 60-100 årig skog.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2400,60 +2273,66 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119161388</v>
+        <v>128370951</v>
       </c>
       <c r="B15" t="n">
-        <v>90056</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5734</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västermoren (Västermoren), Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517065</v>
+        <v>517049</v>
       </c>
       <c r="R15" t="n">
-        <v>6668234</v>
+        <v>6668217</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2477,22 +2356,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2501,78 +2370,95 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127818825</v>
+        <v>128370989</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517119</v>
+        <v>517070</v>
       </c>
       <c r="R16" t="n">
-        <v>6668200</v>
+        <v>6668207</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2596,12 +2482,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2614,65 +2500,99 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127896964</v>
+        <v>95902472</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>91398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5745</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västermoren, Västermoren, Dlr</t>
+          <t>Flogberget gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517078</v>
+        <v>517023</v>
       </c>
       <c r="R17" t="n">
-        <v>6668218</v>
+        <v>6668180</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2696,12 +2616,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>22 + 6 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,72 +2639,104 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>närmast är sälg, rönn, björk, närmaste gran är 3 m.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # närmast är sälg, rönn, björk, närmaste gran är 3 m.</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929383</v>
+        <v>111615078</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>91398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>5745</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517062</v>
+        <v>517019</v>
       </c>
       <c r="R18" t="n">
-        <v>6668237</v>
+        <v>6668195</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2803,12 +2760,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2821,6 +2778,16 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2831,79 +2798,75 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127929400</v>
+        <v>111629560</v>
       </c>
       <c r="B19" t="n">
-        <v>5197</v>
+        <v>91398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>5745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogbergets gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517077</v>
+        <v>517013</v>
       </c>
       <c r="R19" t="n">
-        <v>6668228</v>
+        <v>6668212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2930,12 +2893,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Intill stigen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2944,96 +2922,77 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127929414</v>
+        <v>111776903</v>
       </c>
       <c r="B20" t="n">
-        <v>5002</v>
+        <v>91398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105212</v>
+        <v>5745</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517124</v>
+        <v>517020</v>
       </c>
       <c r="R20" t="n">
-        <v>6668189</v>
+        <v>6668177</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3057,12 +3016,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3075,6 +3034,16 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3085,82 +3054,79 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Martin Gotink</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127929429</v>
+        <v>111776936</v>
       </c>
       <c r="B21" t="n">
-        <v>4773</v>
+        <v>91398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>5745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517205</v>
+        <v>517076</v>
       </c>
       <c r="R21" t="n">
-        <v>6668188</v>
+        <v>6668201</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3184,12 +3150,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3202,6 +3168,16 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3212,86 +3188,79 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Martin Gotink</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127929425</v>
+        <v>111924345</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>91398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>5745</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flogberget, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517205</v>
+        <v>517025</v>
       </c>
       <c r="R22" t="n">
-        <v>6668188</v>
+        <v>6668173</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3315,12 +3284,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4+3 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3333,6 +3307,16 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3343,87 +3327,79 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127929663</v>
+        <v>111924352</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>91398</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517074</v>
+        <v>517031</v>
       </c>
       <c r="R23" t="n">
-        <v>6668246</v>
+        <v>6668184</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3447,17 +3423,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3466,32 +3437,58 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128371010</v>
+        <v>127672526</v>
       </c>
       <c r="B24" t="n">
-        <v>91011</v>
+        <v>91398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3514,7 +3511,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3526,14 +3523,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517080</v>
+        <v>517019</v>
       </c>
       <c r="R24" t="n">
-        <v>6668206</v>
+        <v>6668194</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3560,12 +3557,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3618,51 +3615,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128370986</v>
+        <v>127743866</v>
       </c>
       <c r="B25" t="n">
-        <v>86769</v>
+        <v>91398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergets gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517070</v>
+        <v>517023</v>
       </c>
       <c r="R25" t="n">
-        <v>6668207</v>
+        <v>6668202</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3686,12 +3691,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,12 +3711,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtängsskog</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>Kalkmarkskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3732,26 +3737,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128370967</v>
+        <v>127865695</v>
       </c>
       <c r="B26" t="n">
-        <v>91011</v>
+        <v>91398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3772,28 +3777,20 @@
           <t>R.H.Petersen</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogberget, Flogberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517054</v>
+        <v>517014</v>
       </c>
       <c r="R26" t="n">
-        <v>6668207</v>
+        <v>6668198</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3820,12 +3817,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3838,77 +3845,52 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128370951</v>
+        <v>128370967</v>
       </c>
       <c r="B27" t="n">
-        <v>92448</v>
+        <v>91398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>5745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3920,14 +3902,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517049</v>
+        <v>517054</v>
       </c>
       <c r="R27" t="n">
-        <v>6668217</v>
+        <v>6668207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4012,37 +3994,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128370970</v>
+        <v>128371010</v>
       </c>
       <c r="B28" t="n">
-        <v>91048</v>
+        <v>91398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>5745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4054,17 +4036,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517054</v>
+        <v>517080</v>
       </c>
       <c r="R28" t="n">
-        <v>6668207</v>
+        <v>6668206</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4146,48 +4128,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128370989</v>
+        <v>111614820</v>
       </c>
       <c r="B29" t="n">
-        <v>92448</v>
+        <v>91435</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flogbergs gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517070</v>
+        <v>517222</v>
       </c>
       <c r="R29" t="n">
-        <v>6668207</v>
+        <v>6668175</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4214,12 +4204,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4239,7 +4229,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog, 50-60 årig granplantering</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4265,44 +4255,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128399064</v>
+        <v>111629699</v>
       </c>
       <c r="B30" t="n">
-        <v>92839</v>
+        <v>91435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4311,20 +4301,19 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flogberget gruvområde, nedanför vägen, Dlr</t>
+          <t>Flogbergets gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517057</v>
+        <v>517013</v>
       </c>
       <c r="R30" t="n">
-        <v>6668295</v>
+        <v>6668212</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4348,12 +4337,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4362,81 +4361,55 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128627698</v>
+        <v>111938715</v>
       </c>
       <c r="B31" t="n">
-        <v>92855</v>
+        <v>91435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4448,14 +4421,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
+          <t>Flogberget gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517145</v>
+        <v>517051</v>
       </c>
       <c r="R31" t="n">
-        <v>6668191</v>
+        <v>6668198</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4482,12 +4455,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4507,7 +4480,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>kalkmark</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4540,56 +4513,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128627684</v>
+        <v>118818655</v>
       </c>
       <c r="B32" t="n">
-        <v>87010</v>
+        <v>91435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3739</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
+          <t>Flogbergets gruvområde, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517047</v>
+        <v>517018</v>
       </c>
       <c r="R32" t="n">
-        <v>6668253</v>
+        <v>6668193</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4616,17 +4589,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 + 10 + 1</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4646,7 +4614,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>kalkmark</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4676,6 +4644,2813 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127818118</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flogbergets gruvor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>517025</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6668173</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkmarkskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127865928</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flogberget, Flogberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>517014</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6668198</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128370970</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, nedan vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>517054</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6668207</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>73111023</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>517078</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6668214</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>95730048</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför gruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>517069</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6668225</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111614976</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flogberget gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>517137</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6668196</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111629564</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flogbergets gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>517013</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6668212</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111630451</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flogbergets gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>517156</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6668220</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119159615</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flogberget, Flogberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>517034</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6668185</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gran och björk samt rönn inom 6 meters radie. Grandominerad mark</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127929676</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>517032</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6668194</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128371031</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flogbergs gruvområde, ovanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>517025</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6668205</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128399064</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flogberget gruvområde, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>517057</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6668295</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128627698</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flogberget gruvfält, O om väg 637, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>517145</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6668191</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>111630488</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90721</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6292</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tricholoma viridilutescens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flogbergets gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>517225</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6668199</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127929429</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>517205</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6668188</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127929383</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>517062</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6668237</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127929414</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5004</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>517124</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6668189</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127929400</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>517077</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6668228</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127929425</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>517205</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6668188</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson, Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>111452144</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flogberget gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>517083</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6668221</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>mossig äldre kalkmarksskog,</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127818825</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flogberget, nedanför vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>517119</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6668200</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127929663</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>517074</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6668246</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118818678</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flogbergets gruvområde, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>517023</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6668205</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>kalkgrus</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>mossa</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>mossa</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36532-2025 artfynd.xlsx
+++ b/artfynd/A 36532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111615018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630399</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73111050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103883115</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1294,6 +1319,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111615967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1411,6 +1441,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630395</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1550,6 +1585,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627684</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1676,6 +1716,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95902482</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1802,6 +1847,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370986</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,6 +1952,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127896964</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2036,6 +2091,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96230552</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2143,6 +2203,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111614979</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2277,6 +2342,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399382</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2411,6 +2481,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370951</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2537,6 +2612,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370989</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2681,6 +2761,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95902472</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2815,6 +2900,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111615078</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2937,6 +3027,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111629560</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3071,6 +3166,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111776903</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3205,6 +3305,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111776936</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3344,6 +3449,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111924345</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3478,6 +3588,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111924352</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3612,6 +3727,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127672526</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3746,6 +3866,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743866</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3857,6 +3982,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127865695</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3991,6 +4121,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370967</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4125,6 +4260,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371010</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4259,6 +4399,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111614820</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4376,6 +4521,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111629699</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4510,6 +4660,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111938715</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4644,6 +4799,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118818655</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4773,6 +4933,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127818118</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4880,6 +5045,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127865928</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5014,6 +5184,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370970</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5147,6 +5322,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73111023</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5268,6 +5448,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95730048</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5383,6 +5568,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111614976</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5500,6 +5690,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111629564</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5612,6 +5807,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630451</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5728,6 +5928,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119159615</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5834,6 +6039,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929676</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5968,6 +6178,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371031</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6102,6 +6317,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399064</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6236,6 +6456,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627698</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6353,6 +6578,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630488</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6480,6 +6710,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929429</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6607,6 +6842,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929383</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6734,6 +6974,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929414</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6861,6 +7106,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929400</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6992,6 +7242,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929425</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7104,6 +7359,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111452144</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7214,6 +7474,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127818825</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7330,6 +7595,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929663</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7451,8 +7721,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118818678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>